--- a/config/config_v1.xlsx
+++ b/config/config_v1.xlsx
@@ -5,16 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gameDesign\rollHeroRe\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\buddyWork\rollHeroRe\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="12375" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="hero" sheetId="1" r:id="rId1"/>
     <sheet name="skill" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="tank" sheetId="3" r:id="rId3"/>
+    <sheet name="mage" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="302">
   <si>
     <t>tag</t>
   </si>
@@ -168,6 +169,78 @@
     <t>剑骑士官</t>
   </si>
   <si>
+    <t>guard</t>
+  </si>
+  <si>
+    <t>守卫</t>
+  </si>
+  <si>
+    <t>tank</t>
+  </si>
+  <si>
+    <t>shieldBearer</t>
+  </si>
+  <si>
+    <t>持盾侍从</t>
+  </si>
+  <si>
+    <t>shieldFighter</t>
+  </si>
+  <si>
+    <t>盾斗士</t>
+  </si>
+  <si>
+    <t>shieldGuard</t>
+  </si>
+  <si>
+    <t>盾卫</t>
+  </si>
+  <si>
+    <t>apprenticeKnight</t>
+  </si>
+  <si>
+    <t>见习骑士</t>
+  </si>
+  <si>
+    <t>phalanxSoldier</t>
+  </si>
+  <si>
+    <t>方阵士兵</t>
+  </si>
+  <si>
+    <t>shieldOfficer</t>
+  </si>
+  <si>
+    <t>盾卫士官</t>
+  </si>
+  <si>
+    <t>yellow</t>
+  </si>
+  <si>
+    <t>dualShieldFighter</t>
+  </si>
+  <si>
+    <t>双盾斗士</t>
+  </si>
+  <si>
+    <t>heavyShieldKnight</t>
+  </si>
+  <si>
+    <t>重盾骑士</t>
+  </si>
+  <si>
+    <t>whiteKnight</t>
+  </si>
+  <si>
+    <t>白骑士</t>
+  </si>
+  <si>
+    <t>bulwarkKnight</t>
+  </si>
+  <si>
+    <t>壁垒骑士</t>
+  </si>
+  <si>
     <t>角色</t>
   </si>
   <si>
@@ -370,6 +443,504 @@
   </si>
   <si>
     <t>乱拳连打_连击+1</t>
+  </si>
+  <si>
+    <t>guard_skill1</t>
+  </si>
+  <si>
+    <t>持盾攻击</t>
+  </si>
+  <si>
+    <t>red,1;blue,1</t>
+  </si>
+  <si>
+    <t>shieldBearer_skill1</t>
+  </si>
+  <si>
+    <t>shieldBearer_skill2</t>
+  </si>
+  <si>
+    <t>保护</t>
+  </si>
+  <si>
+    <t>blue,1</t>
+  </si>
+  <si>
+    <t>我方任意单位</t>
+  </si>
+  <si>
+    <t>shieldFighter_skill1</t>
+  </si>
+  <si>
+    <t>持盾突击</t>
+  </si>
+  <si>
+    <t>3+当前护甲值</t>
+  </si>
+  <si>
+    <t>shieldFighter_skill2</t>
+  </si>
+  <si>
+    <t>援护</t>
+  </si>
+  <si>
+    <t>我方任意单位和自身</t>
+  </si>
+  <si>
+    <t>shieldGuard_skill1</t>
+  </si>
+  <si>
+    <t>red,1;blue,2</t>
+  </si>
+  <si>
+    <t>apprenticeKnight_skill1</t>
+  </si>
+  <si>
+    <t>apprenticeKnight_skill2</t>
+  </si>
+  <si>
+    <t>phalanxSoldier_skill1</t>
+  </si>
+  <si>
+    <t>蓄能冲击</t>
+  </si>
+  <si>
+    <t>击杀敌人时自身护甲+3</t>
+  </si>
+  <si>
+    <t>phalanxSoldier_skill2</t>
+  </si>
+  <si>
+    <t>竖守</t>
+  </si>
+  <si>
+    <t>blue,3</t>
+  </si>
+  <si>
+    <t>shieldOfficer_skill1</t>
+  </si>
+  <si>
+    <t>shieldOfficer_skill2</t>
+  </si>
+  <si>
+    <t>dualShieldFighter_skill1</t>
+  </si>
+  <si>
+    <t>二连盾击</t>
+  </si>
+  <si>
+    <t>red,3;blue,2</t>
+  </si>
+  <si>
+    <t>4+当前护甲值</t>
+  </si>
+  <si>
+    <t>dualShieldFighter_skill2</t>
+  </si>
+  <si>
+    <t>blue,3;green,2</t>
+  </si>
+  <si>
+    <t>自身所在列</t>
+  </si>
+  <si>
+    <t>二连盾击_连击+1</t>
+  </si>
+  <si>
+    <t>heavyShieldKnight_skill1</t>
+  </si>
+  <si>
+    <t>重盾猛击</t>
+  </si>
+  <si>
+    <t>自身当前护甲值</t>
+  </si>
+  <si>
+    <t>heavyShieldKnight_skill2</t>
+  </si>
+  <si>
+    <t>阻挡</t>
+  </si>
+  <si>
+    <t>whiteKnight_skill1</t>
+  </si>
+  <si>
+    <t>二连斩击</t>
+  </si>
+  <si>
+    <t>whiteKnight_skill2</t>
+  </si>
+  <si>
+    <t>祈福</t>
+  </si>
+  <si>
+    <t>red,2;blue,2</t>
+  </si>
+  <si>
+    <t>攻击力+2</t>
+  </si>
+  <si>
+    <t>bulwarkKnight_skill1</t>
+  </si>
+  <si>
+    <t>5+当前护甲值</t>
+  </si>
+  <si>
+    <t>bulwarkKnight_skill2</t>
+  </si>
+  <si>
+    <t>壁垒</t>
+  </si>
+  <si>
+    <t>blue,4;green,1</t>
+  </si>
+  <si>
+    <t>自身所在行</t>
+  </si>
+  <si>
+    <t>apprentice</t>
+  </si>
+  <si>
+    <t>学徒</t>
+  </si>
+  <si>
+    <t>mage</t>
+  </si>
+  <si>
+    <t>red</t>
+  </si>
+  <si>
+    <t>green</t>
+  </si>
+  <si>
+    <t>flameApprentice</t>
+  </si>
+  <si>
+    <t>烈焰学徒</t>
+  </si>
+  <si>
+    <t>thunderApprentice</t>
+  </si>
+  <si>
+    <t>雷语学徒</t>
+  </si>
+  <si>
+    <t>frostApprentice</t>
+  </si>
+  <si>
+    <t>寒冰学徒</t>
+  </si>
+  <si>
+    <t>blue</t>
+  </si>
+  <si>
+    <t>flameSwordsman</t>
+  </si>
+  <si>
+    <t>炎剑士</t>
+  </si>
+  <si>
+    <t>thunderAcolyte</t>
+  </si>
+  <si>
+    <t>雷霆侍僧</t>
+  </si>
+  <si>
+    <t>frostAcolyte</t>
+  </si>
+  <si>
+    <t>寒霜侍僧</t>
+  </si>
+  <si>
+    <t>blazeMage</t>
+  </si>
+  <si>
+    <t>爆炎术士</t>
+  </si>
+  <si>
+    <t>thunderMage</t>
+  </si>
+  <si>
+    <t>雷语法师</t>
+  </si>
+  <si>
+    <t>frostMage</t>
+  </si>
+  <si>
+    <t>寒冰法师</t>
+  </si>
+  <si>
+    <t>blazeSwordsman</t>
+  </si>
+  <si>
+    <t>爆炎剑士</t>
+  </si>
+  <si>
+    <t>thunderPriest</t>
+  </si>
+  <si>
+    <t>雷霆祭司</t>
+  </si>
+  <si>
+    <t>frostPriest</t>
+  </si>
+  <si>
+    <t>寒霜祭司</t>
+  </si>
+  <si>
+    <t>apprentice_skill1</t>
+  </si>
+  <si>
+    <t>火球</t>
+  </si>
+  <si>
+    <t>red,1;blue,1</t>
+  </si>
+  <si>
+    <t>任意目标</t>
+  </si>
+  <si>
+    <t>选择目标</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>flameApprentice_skill1</t>
+  </si>
+  <si>
+    <t>大火球</t>
+  </si>
+  <si>
+    <t>red,1;blue,2</t>
+  </si>
+  <si>
+    <t>thunderApprentice_skill1</t>
+  </si>
+  <si>
+    <t>雷电术</t>
+  </si>
+  <si>
+    <t>green,2</t>
+  </si>
+  <si>
+    <t>thunderApprentice_skill2</t>
+  </si>
+  <si>
+    <t>静电</t>
+  </si>
+  <si>
+    <t>red,2;blue,1</t>
+  </si>
+  <si>
+    <t>自身</t>
+  </si>
+  <si>
+    <t>自动</t>
+  </si>
+  <si>
+    <t>雷电术_充能+1</t>
+  </si>
+  <si>
+    <t>frostApprentice_skill1</t>
+  </si>
+  <si>
+    <t>冰箭术</t>
+  </si>
+  <si>
+    <t>red,1;blue,1;green,1</t>
+  </si>
+  <si>
+    <t>frostApprentice_skill2</t>
+  </si>
+  <si>
+    <t>冷却</t>
+  </si>
+  <si>
+    <t>green,3</t>
+  </si>
+  <si>
+    <t>攻击力+4</t>
+  </si>
+  <si>
+    <t>flameSwordsman_skill1</t>
+  </si>
+  <si>
+    <t>烈焰横扫</t>
+  </si>
+  <si>
+    <t>近战目标及同行</t>
+  </si>
+  <si>
+    <t>flameSwordsman_skill2</t>
+  </si>
+  <si>
+    <t>red,2</t>
+  </si>
+  <si>
+    <t>thunderAcolyte_skill1</t>
+  </si>
+  <si>
+    <t>闪电链</t>
+  </si>
+  <si>
+    <t>近战目标和1个随机目标</t>
+  </si>
+  <si>
+    <t>thunderAcolyte_skill2</t>
+  </si>
+  <si>
+    <t>超载</t>
+  </si>
+  <si>
+    <t>blue,2</t>
+  </si>
+  <si>
+    <t>闪电链_随机目标+1</t>
+  </si>
+  <si>
+    <t>frostAcolyte_skill1</t>
+  </si>
+  <si>
+    <t>冰锥术</t>
+  </si>
+  <si>
+    <t>blue,1;green,2</t>
+  </si>
+  <si>
+    <t>frostAcolyte_skill1_sub</t>
+  </si>
+  <si>
+    <t>相邻单位</t>
+  </si>
+  <si>
+    <t>frostAcolyte_skill2</t>
+  </si>
+  <si>
+    <t>霜盾</t>
+  </si>
+  <si>
+    <t>自身所在列</t>
+  </si>
+  <si>
+    <t>blazeMage_skill1</t>
+  </si>
+  <si>
+    <t>red,1;blue,3</t>
+  </si>
+  <si>
+    <t>blazeMage_skill2</t>
+  </si>
+  <si>
+    <t>爆炎火球</t>
+  </si>
+  <si>
+    <t>green,5</t>
+  </si>
+  <si>
+    <t>任意目标及相邻单位</t>
+  </si>
+  <si>
+    <t>thunderMage_skill1</t>
+  </si>
+  <si>
+    <t>轰雷术</t>
+  </si>
+  <si>
+    <t>thunderMage_skill1_sub</t>
+  </si>
+  <si>
+    <t>thunderMage_skill2</t>
+  </si>
+  <si>
+    <t>red,3;blue,2</t>
+  </si>
+  <si>
+    <t>轰雷术_充能+1</t>
+  </si>
+  <si>
+    <t>frostMage_skill1</t>
+  </si>
+  <si>
+    <t>冰枪术</t>
+  </si>
+  <si>
+    <t>blue,1;green,3</t>
+  </si>
+  <si>
+    <t>frostMage_skill1_sub</t>
+  </si>
+  <si>
+    <t>冰枪术_充能+1</t>
+  </si>
+  <si>
+    <t>frostMage_skill2</t>
+  </si>
+  <si>
+    <t>攻击力+6</t>
+  </si>
+  <si>
+    <t>blazeSwordsman_skill1</t>
+  </si>
+  <si>
+    <t>烈焰魔剑</t>
+  </si>
+  <si>
+    <t>red,2;green,4</t>
+  </si>
+  <si>
+    <t>blazeSwordsman_skill2</t>
+  </si>
+  <si>
+    <t>怒焰魔剑</t>
+  </si>
+  <si>
+    <t>blue,4;green,2</t>
+  </si>
+  <si>
+    <t>任意列</t>
+  </si>
+  <si>
+    <t>thunderPriest_skill1</t>
+  </si>
+  <si>
+    <t>大闪电链</t>
+  </si>
+  <si>
+    <t>green,4</t>
+  </si>
+  <si>
+    <t>近战目标和2个随机目标</t>
+  </si>
+  <si>
+    <t>thunderPriest_skill2</t>
+  </si>
+  <si>
+    <t>red,2;blue,2</t>
+  </si>
+  <si>
+    <t>攻击力+2;大闪电链_随机目标+2</t>
+  </si>
+  <si>
+    <t>frostPriest_skill1</t>
+  </si>
+  <si>
+    <t>冰暴术</t>
+  </si>
+  <si>
+    <t>frostPriest_skill2</t>
+  </si>
+  <si>
+    <t>blue,3;green,3</t>
+  </si>
+  <si>
+    <t>自身及相邻单位</t>
+  </si>
+  <si>
+    <t>phalanxSoldier_skill1_sub</t>
+  </si>
+  <si>
+    <t>方阵士兵</t>
   </si>
 </sst>
 </file>
@@ -1517,6 +2088,1024 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2743200" y="1028700"/>
+          <a:ext cx="3800475" cy="3276600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6858000" y="1028700"/>
+          <a:ext cx="3848100" cy="5029200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="图片 4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10972800" y="1028700"/>
+          <a:ext cx="3876675" cy="4933950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="图片 5"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19659600" y="1028700"/>
+          <a:ext cx="3886200" cy="4924425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="图片 6"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="23774400" y="1028700"/>
+          <a:ext cx="3952875" cy="5057775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="图片 7"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15087600" y="1028700"/>
+          <a:ext cx="3971925" cy="3352800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="图片 8"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2743200" y="5657850"/>
+          <a:ext cx="3933825" cy="4867275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="图片 9"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6858000" y="6343650"/>
+          <a:ext cx="3981450" cy="4962525"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="图片 10"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10972800" y="6343650"/>
+          <a:ext cx="3829050" cy="4810125"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>638175</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="图片 11"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15087600" y="6343650"/>
+          <a:ext cx="4067175" cy="4953000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="图片 12"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19202400" y="6343650"/>
+          <a:ext cx="3962400" cy="4991100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2057400" y="342900"/>
+          <a:ext cx="3981450" cy="3333750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2057400" y="3771900"/>
+          <a:ext cx="3962400" cy="3286125"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6172200" y="3771900"/>
+          <a:ext cx="3962400" cy="4962525"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="图片 4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10287000" y="3771900"/>
+          <a:ext cx="3962400" cy="4924425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="图片 5"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14401800" y="3771900"/>
+          <a:ext cx="3943350" cy="5019675"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="图片 6"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18516600" y="3771900"/>
+          <a:ext cx="3943350" cy="4857750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="图片 7"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="22631400" y="3771900"/>
+          <a:ext cx="3962400" cy="4981575"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="图片 8"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2057400" y="9429750"/>
+          <a:ext cx="3914775" cy="5000625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="图片 9"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6172200" y="9258300"/>
+          <a:ext cx="4057650" cy="5076825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="图片 10"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10287000" y="9258300"/>
+          <a:ext cx="3943350" cy="4886325"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="图片 11"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14401800" y="9258300"/>
+          <a:ext cx="4048125" cy="4962525"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="图片 12"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18516600" y="9258300"/>
+          <a:ext cx="4029075" cy="5000625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="图片 13"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="22631400" y="9258300"/>
+          <a:ext cx="4038600" cy="5067300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
@@ -1767,7 +3356,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:S36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="5" max="10" width="10.375" customWidth="1"/>
@@ -2442,6 +4031,1278 @@
         <v>10</v>
       </c>
       <c r="R12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>7</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
+      <c r="A14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14">
+        <v>2</v>
+      </c>
+      <c r="L14">
+        <v>2</v>
+      </c>
+      <c r="M14">
+        <v>2</v>
+      </c>
+      <c r="N14">
+        <v>2</v>
+      </c>
+      <c r="O14">
+        <v>2</v>
+      </c>
+      <c r="P14">
+        <v>2</v>
+      </c>
+      <c r="Q14">
+        <v>9</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
+      <c r="A15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>2</v>
+      </c>
+      <c r="O15">
+        <v>2</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>8</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
+      <c r="A16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>2</v>
+      </c>
+      <c r="N16">
+        <v>2</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>8</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>2</v>
+      </c>
+      <c r="N17">
+        <v>2</v>
+      </c>
+      <c r="O17">
+        <v>2</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>8</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" t="s">
+        <v>22</v>
+      </c>
+      <c r="H18" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>2</v>
+      </c>
+      <c r="M18">
+        <v>2</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>9</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
+      <c r="A19" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" t="s">
+        <v>22</v>
+      </c>
+      <c r="H19" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" t="s">
+        <v>59</v>
+      </c>
+      <c r="K19">
+        <v>3</v>
+      </c>
+      <c r="L19">
+        <v>3</v>
+      </c>
+      <c r="M19">
+        <v>3</v>
+      </c>
+      <c r="N19">
+        <v>3</v>
+      </c>
+      <c r="O19">
+        <v>3</v>
+      </c>
+      <c r="P19">
+        <v>1</v>
+      </c>
+      <c r="Q19">
+        <v>12</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
+      <c r="A20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20" t="s">
+        <v>22</v>
+      </c>
+      <c r="K20">
+        <v>3</v>
+      </c>
+      <c r="L20">
+        <v>3</v>
+      </c>
+      <c r="M20">
+        <v>2</v>
+      </c>
+      <c r="N20">
+        <v>2</v>
+      </c>
+      <c r="O20">
+        <v>2</v>
+      </c>
+      <c r="P20">
+        <v>2</v>
+      </c>
+      <c r="Q20">
+        <v>11</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
+      <c r="A21" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" t="s">
+        <v>22</v>
+      </c>
+      <c r="H21" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" t="s">
+        <v>22</v>
+      </c>
+      <c r="K21">
+        <v>2</v>
+      </c>
+      <c r="L21">
+        <v>3</v>
+      </c>
+      <c r="M21">
+        <v>3</v>
+      </c>
+      <c r="N21">
+        <v>2</v>
+      </c>
+      <c r="O21">
+        <v>2</v>
+      </c>
+      <c r="P21">
+        <v>2</v>
+      </c>
+      <c r="Q21">
+        <v>10</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="A22" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" t="s">
+        <v>22</v>
+      </c>
+      <c r="I22" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" t="s">
+        <v>35</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>3</v>
+      </c>
+      <c r="M22">
+        <v>3</v>
+      </c>
+      <c r="N22">
+        <v>2</v>
+      </c>
+      <c r="O22">
+        <v>2</v>
+      </c>
+      <c r="P22">
+        <v>2</v>
+      </c>
+      <c r="Q22">
+        <v>10</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" t="s">
+        <v>22</v>
+      </c>
+      <c r="I23" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" t="s">
+        <v>35</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>4</v>
+      </c>
+      <c r="M23">
+        <v>3</v>
+      </c>
+      <c r="N23">
+        <v>3</v>
+      </c>
+      <c r="O23">
+        <v>2</v>
+      </c>
+      <c r="P23">
+        <v>1</v>
+      </c>
+      <c r="Q23">
+        <v>11</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
+      <c r="A24" t="s">
+        <v>187</v>
+      </c>
+      <c r="B24" t="s">
+        <v>188</v>
+      </c>
+      <c r="C24" t="s">
+        <v>189</v>
+      </c>
+      <c r="E24" t="s">
+        <v>190</v>
+      </c>
+      <c r="F24" t="s">
+        <v>190</v>
+      </c>
+      <c r="G24" t="s">
+        <v>191</v>
+      </c>
+      <c r="H24" t="s">
+        <v>191</v>
+      </c>
+      <c r="I24" t="s">
+        <v>191</v>
+      </c>
+      <c r="J24" t="s">
+        <v>191</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="O24">
+        <v>1</v>
+      </c>
+      <c r="P24">
+        <v>1</v>
+      </c>
+      <c r="Q24">
+        <v>3</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
+      <c r="A25" t="s">
+        <v>192</v>
+      </c>
+      <c r="B25" t="s">
+        <v>193</v>
+      </c>
+      <c r="C25" t="s">
+        <v>189</v>
+      </c>
+      <c r="E25" t="s">
+        <v>190</v>
+      </c>
+      <c r="F25" t="s">
+        <v>190</v>
+      </c>
+      <c r="G25" t="s">
+        <v>191</v>
+      </c>
+      <c r="H25" t="s">
+        <v>191</v>
+      </c>
+      <c r="I25" t="s">
+        <v>191</v>
+      </c>
+      <c r="J25" t="s">
+        <v>191</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25">
+        <v>2</v>
+      </c>
+      <c r="N25">
+        <v>2</v>
+      </c>
+      <c r="O25">
+        <v>1</v>
+      </c>
+      <c r="P25">
+        <v>1</v>
+      </c>
+      <c r="Q25">
+        <v>4</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
+      <c r="A26" t="s">
+        <v>194</v>
+      </c>
+      <c r="B26" t="s">
+        <v>195</v>
+      </c>
+      <c r="C26" t="s">
+        <v>189</v>
+      </c>
+      <c r="E26" t="s">
+        <v>190</v>
+      </c>
+      <c r="F26" t="s">
+        <v>191</v>
+      </c>
+      <c r="G26" t="s">
+        <v>191</v>
+      </c>
+      <c r="H26" t="s">
+        <v>191</v>
+      </c>
+      <c r="I26" t="s">
+        <v>191</v>
+      </c>
+      <c r="J26" t="s">
+        <v>191</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>2</v>
+      </c>
+      <c r="M26">
+        <v>2</v>
+      </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
+      <c r="O26">
+        <v>1</v>
+      </c>
+      <c r="P26">
+        <v>1</v>
+      </c>
+      <c r="Q26">
+        <v>4</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
+      <c r="A27" t="s">
+        <v>196</v>
+      </c>
+      <c r="B27" t="s">
+        <v>197</v>
+      </c>
+      <c r="C27" t="s">
+        <v>189</v>
+      </c>
+      <c r="E27" t="s">
+        <v>190</v>
+      </c>
+      <c r="F27" t="s">
+        <v>198</v>
+      </c>
+      <c r="G27" t="s">
+        <v>198</v>
+      </c>
+      <c r="H27" t="s">
+        <v>191</v>
+      </c>
+      <c r="I27" t="s">
+        <v>191</v>
+      </c>
+      <c r="J27" t="s">
+        <v>191</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
+      </c>
+      <c r="N27">
+        <v>2</v>
+      </c>
+      <c r="O27">
+        <v>2</v>
+      </c>
+      <c r="P27">
+        <v>1</v>
+      </c>
+      <c r="Q27">
+        <v>6</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19">
+      <c r="A28" t="s">
+        <v>199</v>
+      </c>
+      <c r="B28" t="s">
+        <v>200</v>
+      </c>
+      <c r="C28" t="s">
+        <v>189</v>
+      </c>
+      <c r="E28" t="s">
+        <v>190</v>
+      </c>
+      <c r="F28" t="s">
+        <v>190</v>
+      </c>
+      <c r="G28" t="s">
+        <v>190</v>
+      </c>
+      <c r="H28" t="s">
+        <v>191</v>
+      </c>
+      <c r="I28" t="s">
+        <v>191</v>
+      </c>
+      <c r="J28" t="s">
+        <v>191</v>
+      </c>
+      <c r="K28">
+        <v>2</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>1</v>
+      </c>
+      <c r="N28">
+        <v>2</v>
+      </c>
+      <c r="O28">
+        <v>1</v>
+      </c>
+      <c r="P28">
+        <v>1</v>
+      </c>
+      <c r="Q28">
+        <v>6</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
+      <c r="A29" t="s">
+        <v>201</v>
+      </c>
+      <c r="B29" t="s">
+        <v>202</v>
+      </c>
+      <c r="C29" t="s">
+        <v>189</v>
+      </c>
+      <c r="E29" t="s">
+        <v>190</v>
+      </c>
+      <c r="F29" t="s">
+        <v>198</v>
+      </c>
+      <c r="G29" t="s">
+        <v>191</v>
+      </c>
+      <c r="H29" t="s">
+        <v>191</v>
+      </c>
+      <c r="I29" t="s">
+        <v>191</v>
+      </c>
+      <c r="J29" t="s">
+        <v>191</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="M29">
+        <v>2</v>
+      </c>
+      <c r="N29">
+        <v>2</v>
+      </c>
+      <c r="O29">
+        <v>1</v>
+      </c>
+      <c r="P29">
+        <v>1</v>
+      </c>
+      <c r="Q29">
+        <v>4</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
+      <c r="A30" t="s">
+        <v>203</v>
+      </c>
+      <c r="B30" t="s">
+        <v>204</v>
+      </c>
+      <c r="C30" t="s">
+        <v>189</v>
+      </c>
+      <c r="E30" t="s">
+        <v>198</v>
+      </c>
+      <c r="F30" t="s">
+        <v>198</v>
+      </c>
+      <c r="G30" t="s">
+        <v>191</v>
+      </c>
+      <c r="H30" t="s">
+        <v>191</v>
+      </c>
+      <c r="I30" t="s">
+        <v>191</v>
+      </c>
+      <c r="J30" t="s">
+        <v>191</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30">
+        <v>1</v>
+      </c>
+      <c r="M30">
+        <v>2</v>
+      </c>
+      <c r="N30">
+        <v>2</v>
+      </c>
+      <c r="O30">
+        <v>1</v>
+      </c>
+      <c r="P30">
+        <v>1</v>
+      </c>
+      <c r="Q30">
+        <v>5</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19">
+      <c r="A31" t="s">
+        <v>205</v>
+      </c>
+      <c r="B31" t="s">
+        <v>206</v>
+      </c>
+      <c r="C31" t="s">
+        <v>189</v>
+      </c>
+      <c r="E31" t="s">
+        <v>190</v>
+      </c>
+      <c r="F31" t="s">
+        <v>190</v>
+      </c>
+      <c r="G31" t="s">
+        <v>191</v>
+      </c>
+      <c r="H31" t="s">
+        <v>191</v>
+      </c>
+      <c r="I31" t="s">
+        <v>191</v>
+      </c>
+      <c r="J31" t="s">
+        <v>191</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31">
+        <v>1</v>
+      </c>
+      <c r="M31">
+        <v>3</v>
+      </c>
+      <c r="N31">
+        <v>3</v>
+      </c>
+      <c r="O31">
+        <v>3</v>
+      </c>
+      <c r="P31">
+        <v>2</v>
+      </c>
+      <c r="Q31">
+        <v>6</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19">
+      <c r="A32" t="s">
+        <v>207</v>
+      </c>
+      <c r="B32" t="s">
+        <v>208</v>
+      </c>
+      <c r="C32" t="s">
+        <v>189</v>
+      </c>
+      <c r="E32" t="s">
+        <v>190</v>
+      </c>
+      <c r="F32" t="s">
+        <v>191</v>
+      </c>
+      <c r="G32" t="s">
+        <v>191</v>
+      </c>
+      <c r="H32" t="s">
+        <v>191</v>
+      </c>
+      <c r="I32" t="s">
+        <v>191</v>
+      </c>
+      <c r="J32" t="s">
+        <v>191</v>
+      </c>
+      <c r="K32">
+        <v>2</v>
+      </c>
+      <c r="L32">
+        <v>3</v>
+      </c>
+      <c r="M32">
+        <v>3</v>
+      </c>
+      <c r="N32">
+        <v>3</v>
+      </c>
+      <c r="O32">
+        <v>2</v>
+      </c>
+      <c r="P32">
+        <v>1</v>
+      </c>
+      <c r="Q32">
+        <v>6</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
+      <c r="A33" t="s">
+        <v>209</v>
+      </c>
+      <c r="B33" t="s">
+        <v>210</v>
+      </c>
+      <c r="C33" t="s">
+        <v>189</v>
+      </c>
+      <c r="E33" t="s">
+        <v>198</v>
+      </c>
+      <c r="F33" t="s">
+        <v>198</v>
+      </c>
+      <c r="G33" t="s">
+        <v>191</v>
+      </c>
+      <c r="H33" t="s">
+        <v>191</v>
+      </c>
+      <c r="I33" t="s">
+        <v>191</v>
+      </c>
+      <c r="J33" t="s">
+        <v>191</v>
+      </c>
+      <c r="K33">
+        <v>2</v>
+      </c>
+      <c r="L33">
+        <v>2</v>
+      </c>
+      <c r="M33">
+        <v>3</v>
+      </c>
+      <c r="N33">
+        <v>3</v>
+      </c>
+      <c r="O33">
+        <v>3</v>
+      </c>
+      <c r="P33">
+        <v>2</v>
+      </c>
+      <c r="Q33">
+        <v>8</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
+      <c r="A34" t="s">
+        <v>211</v>
+      </c>
+      <c r="B34" t="s">
+        <v>212</v>
+      </c>
+      <c r="C34" t="s">
+        <v>189</v>
+      </c>
+      <c r="E34" t="s">
+        <v>190</v>
+      </c>
+      <c r="F34" t="s">
+        <v>190</v>
+      </c>
+      <c r="G34" t="s">
+        <v>190</v>
+      </c>
+      <c r="H34" t="s">
+        <v>191</v>
+      </c>
+      <c r="I34" t="s">
+        <v>191</v>
+      </c>
+      <c r="J34" t="s">
+        <v>191</v>
+      </c>
+      <c r="K34">
+        <v>2</v>
+      </c>
+      <c r="L34">
+        <v>2</v>
+      </c>
+      <c r="M34">
+        <v>2</v>
+      </c>
+      <c r="N34">
+        <v>3</v>
+      </c>
+      <c r="O34">
+        <v>3</v>
+      </c>
+      <c r="P34">
+        <v>2</v>
+      </c>
+      <c r="Q34">
+        <v>8</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19">
+      <c r="A35" t="s">
+        <v>213</v>
+      </c>
+      <c r="B35" t="s">
+        <v>214</v>
+      </c>
+      <c r="C35" t="s">
+        <v>189</v>
+      </c>
+      <c r="E35" t="s">
+        <v>190</v>
+      </c>
+      <c r="F35" t="s">
+        <v>198</v>
+      </c>
+      <c r="G35" t="s">
+        <v>191</v>
+      </c>
+      <c r="H35" t="s">
+        <v>191</v>
+      </c>
+      <c r="I35" t="s">
+        <v>191</v>
+      </c>
+      <c r="J35" t="s">
+        <v>191</v>
+      </c>
+      <c r="K35">
+        <v>2</v>
+      </c>
+      <c r="L35">
+        <v>2</v>
+      </c>
+      <c r="M35">
+        <v>3</v>
+      </c>
+      <c r="N35">
+        <v>3</v>
+      </c>
+      <c r="O35">
+        <v>2</v>
+      </c>
+      <c r="P35">
+        <v>1</v>
+      </c>
+      <c r="Q35">
+        <v>7</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19">
+      <c r="A36" t="s">
+        <v>215</v>
+      </c>
+      <c r="B36" t="s">
+        <v>216</v>
+      </c>
+      <c r="C36" t="s">
+        <v>189</v>
+      </c>
+      <c r="E36" t="s">
+        <v>190</v>
+      </c>
+      <c r="F36" t="s">
+        <v>198</v>
+      </c>
+      <c r="G36" t="s">
+        <v>198</v>
+      </c>
+      <c r="H36" t="s">
+        <v>191</v>
+      </c>
+      <c r="I36" t="s">
+        <v>191</v>
+      </c>
+      <c r="J36" t="s">
+        <v>191</v>
+      </c>
+      <c r="K36">
+        <v>1</v>
+      </c>
+      <c r="L36">
+        <v>3</v>
+      </c>
+      <c r="M36">
+        <v>2</v>
+      </c>
+      <c r="N36">
+        <v>3</v>
+      </c>
+      <c r="O36">
+        <v>3</v>
+      </c>
+      <c r="P36">
+        <v>3</v>
+      </c>
+      <c r="Q36">
+        <v>8</v>
+      </c>
+      <c r="R36">
         <v>0</v>
       </c>
     </row>
@@ -2456,7 +5317,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -2464,51 +5325,51 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="C1" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="D1" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="E1" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="F1" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="G1" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="H1" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="I1" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="J1" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -2517,30 +5378,30 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="J2" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="G3">
         <v>9</v>
@@ -2549,30 +5410,30 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="J3" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="G4">
         <v>12</v>
@@ -2581,30 +5442,30 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="J4" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="G5">
         <v>7</v>
@@ -2613,30 +5474,30 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="J5" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -2645,30 +5506,30 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="J6" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="B7" t="s">
         <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="G7">
         <v>8</v>
@@ -2677,30 +5538,30 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="J7" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="B8" t="s">
         <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="G8">
         <v>12</v>
@@ -2709,62 +5570,62 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="J8" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s">
         <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="F9" t="s">
+        <v>106</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" t="s">
+        <v>107</v>
+      </c>
+      <c r="J9" t="s">
         <v>82</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9" t="s">
-        <v>83</v>
-      </c>
-      <c r="J9" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="B10" t="s">
         <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="G10">
         <v>18</v>
@@ -2773,30 +5634,30 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="J10" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s">
         <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="F11" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2805,30 +5666,30 @@
         <v>6</v>
       </c>
       <c r="I11" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="J11" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s">
         <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="G12">
         <v>11</v>
@@ -2837,62 +5698,62 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="J12" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="B13" t="s">
         <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="D13" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="F13" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13" t="s">
+        <v>118</v>
+      </c>
+      <c r="J13" t="s">
         <v>82</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13" t="s">
-        <v>94</v>
-      </c>
-      <c r="J13" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s">
         <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
+        <v>104</v>
+      </c>
+      <c r="E14" t="s">
         <v>80</v>
       </c>
-      <c r="E14" t="s">
-        <v>56</v>
-      </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="G14">
         <v>7</v>
@@ -2901,30 +5762,30 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="J14" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s">
         <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="D15" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="E15" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="F15" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2933,30 +5794,30 @@
         <v>3</v>
       </c>
       <c r="I15" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="J15" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="B16" t="s">
         <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="E16" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2965,30 +5826,30 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="J16" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="B17" t="s">
         <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="D17" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="E17" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="G17">
         <v>4</v>
@@ -2997,42 +5858,1610 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="J17" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="B18" t="s">
         <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="D18" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="E18" t="s">
+        <v>105</v>
+      </c>
+      <c r="F18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18" t="s">
+        <v>135</v>
+      </c>
+      <c r="J18" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" t="s">
+        <v>137</v>
+      </c>
+      <c r="D19" t="s">
+        <v>138</v>
+      </c>
+      <c r="E19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" t="s">
         <v>81</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G19">
+        <v>3</v>
+      </c>
+      <c r="H19">
+        <v>3</v>
+      </c>
+      <c r="I19" t="s">
         <v>82</v>
       </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18" t="s">
-        <v>111</v>
-      </c>
-      <c r="J18" t="s">
+      <c r="J19" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" t="s">
+        <v>139</v>
+      </c>
+      <c r="B20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G20">
+        <v>7</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20" t="s">
+        <v>82</v>
+      </c>
+      <c r="J20" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" t="s">
+        <v>140</v>
+      </c>
+      <c r="B21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" t="s">
+        <v>141</v>
+      </c>
+      <c r="D21" t="s">
+        <v>142</v>
+      </c>
+      <c r="E21" t="s">
+        <v>143</v>
+      </c>
+      <c r="F21" t="s">
+        <v>106</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>4</v>
+      </c>
+      <c r="I21" t="s">
+        <v>82</v>
+      </c>
+      <c r="J21" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" t="s">
+        <v>144</v>
+      </c>
+      <c r="B22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" t="s">
+        <v>145</v>
+      </c>
+      <c r="D22" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22" t="s">
+        <v>81</v>
+      </c>
+      <c r="G22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22" t="s">
+        <v>82</v>
+      </c>
+      <c r="J22" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" t="s">
+        <v>147</v>
+      </c>
+      <c r="B23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" t="s">
+        <v>148</v>
+      </c>
+      <c r="D23" t="s">
+        <v>112</v>
+      </c>
+      <c r="E23" t="s">
+        <v>149</v>
+      </c>
+      <c r="F23" t="s">
+        <v>106</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>3</v>
+      </c>
+      <c r="I23" t="s">
+        <v>82</v>
+      </c>
+      <c r="J23" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" t="s">
+        <v>150</v>
+      </c>
+      <c r="B24" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" t="s">
+        <v>137</v>
+      </c>
+      <c r="D24" t="s">
+        <v>151</v>
+      </c>
+      <c r="E24" t="s">
+        <v>80</v>
+      </c>
+      <c r="F24" t="s">
+        <v>81</v>
+      </c>
+      <c r="G24">
+        <v>9</v>
+      </c>
+      <c r="H24">
+        <v>5</v>
+      </c>
+      <c r="I24" t="s">
+        <v>82</v>
+      </c>
+      <c r="J24" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" t="s">
+        <v>152</v>
+      </c>
+      <c r="B25" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E25" t="s">
+        <v>80</v>
+      </c>
+      <c r="F25" t="s">
+        <v>81</v>
+      </c>
+      <c r="G25">
+        <v>6</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25" t="s">
+        <v>82</v>
+      </c>
+      <c r="J25" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" t="s">
+        <v>153</v>
+      </c>
+      <c r="B26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" t="s">
+        <v>148</v>
+      </c>
+      <c r="D26" t="s">
+        <v>112</v>
+      </c>
+      <c r="E26" t="s">
+        <v>149</v>
+      </c>
+      <c r="F26" t="s">
+        <v>106</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>3</v>
+      </c>
+      <c r="I26" t="s">
+        <v>82</v>
+      </c>
+      <c r="J26" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" t="s">
+        <v>154</v>
+      </c>
+      <c r="B27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" t="s">
+        <v>155</v>
+      </c>
+      <c r="D27" t="s">
+        <v>138</v>
+      </c>
+      <c r="E27" t="s">
+        <v>80</v>
+      </c>
+      <c r="F27" t="s">
+        <v>81</v>
+      </c>
+      <c r="G27">
+        <v>7</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27" t="s">
+        <v>156</v>
+      </c>
+      <c r="J27" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" t="s">
+        <v>154</v>
+      </c>
+      <c r="B27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" t="s">
+        <v>155</v>
+      </c>
+      <c r="D27" t="s">
+        <v>138</v>
+      </c>
+      <c r="E27" t="s">
+        <v>80</v>
+      </c>
+      <c r="F27" t="s">
+        <v>81</v>
+      </c>
+      <c r="G27">
+        <v>7</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27" t="s">
+        <v>222</v>
+      </c>
+      <c r="J27" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" t="s">
+        <v>300</v>
+      </c>
+      <c r="B28" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" t="s">
+        <v>105</v>
+      </c>
+      <c r="F28" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>3</v>
+      </c>
+      <c r="I28" t="s">
+        <v>82</v>
+      </c>
+      <c r="J28" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" t="s">
+        <v>157</v>
+      </c>
+      <c r="B29" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" t="s">
+        <v>158</v>
+      </c>
+      <c r="D29" t="s">
+        <v>159</v>
+      </c>
+      <c r="E29" t="s">
+        <v>126</v>
+      </c>
+      <c r="F29" t="s">
+        <v>106</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>4</v>
+      </c>
+      <c r="I29" t="s">
+        <v>82</v>
+      </c>
+      <c r="J29" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" t="s">
+        <v>160</v>
+      </c>
+      <c r="B30" t="s">
         <v>58</v>
+      </c>
+      <c r="C30" t="s">
+        <v>78</v>
+      </c>
+      <c r="D30" t="s">
+        <v>91</v>
+      </c>
+      <c r="E30" t="s">
+        <v>80</v>
+      </c>
+      <c r="F30" t="s">
+        <v>81</v>
+      </c>
+      <c r="G30">
+        <v>8</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30" t="s">
+        <v>82</v>
+      </c>
+      <c r="J30" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" t="s">
+        <v>161</v>
+      </c>
+      <c r="B31" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" t="s">
+        <v>148</v>
+      </c>
+      <c r="D31" t="s">
+        <v>117</v>
+      </c>
+      <c r="E31" t="s">
+        <v>143</v>
+      </c>
+      <c r="F31" t="s">
+        <v>106</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>5</v>
+      </c>
+      <c r="I31" t="s">
+        <v>82</v>
+      </c>
+      <c r="J31" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" t="s">
+        <v>162</v>
+      </c>
+      <c r="B32" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D32" t="s">
+        <v>164</v>
+      </c>
+      <c r="E32" t="s">
+        <v>80</v>
+      </c>
+      <c r="F32" t="s">
+        <v>81</v>
+      </c>
+      <c r="G32" t="s">
+        <v>165</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32" t="s">
+        <v>96</v>
+      </c>
+      <c r="J32" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" t="s">
+        <v>166</v>
+      </c>
+      <c r="B33" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" t="s">
+        <v>103</v>
+      </c>
+      <c r="D33" t="s">
+        <v>167</v>
+      </c>
+      <c r="E33" t="s">
+        <v>168</v>
+      </c>
+      <c r="F33" t="s">
+        <v>106</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>7</v>
+      </c>
+      <c r="I33" t="s">
+        <v>169</v>
+      </c>
+      <c r="J33" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" t="s">
+        <v>170</v>
+      </c>
+      <c r="B34" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" t="s">
+        <v>171</v>
+      </c>
+      <c r="D34" t="s">
+        <v>124</v>
+      </c>
+      <c r="E34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F34" t="s">
+        <v>81</v>
+      </c>
+      <c r="G34" t="s">
+        <v>172</v>
+      </c>
+      <c r="H34">
+        <v>6</v>
+      </c>
+      <c r="I34" t="s">
+        <v>82</v>
+      </c>
+      <c r="J34" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" t="s">
+        <v>173</v>
+      </c>
+      <c r="B35" t="s">
+        <v>63</v>
+      </c>
+      <c r="C35" t="s">
+        <v>174</v>
+      </c>
+      <c r="D35" t="s">
+        <v>151</v>
+      </c>
+      <c r="E35" t="s">
+        <v>168</v>
+      </c>
+      <c r="F35" t="s">
+        <v>106</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>5</v>
+      </c>
+      <c r="I35" t="s">
+        <v>82</v>
+      </c>
+      <c r="J35" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" t="s">
+        <v>175</v>
+      </c>
+      <c r="B36" t="s">
+        <v>65</v>
+      </c>
+      <c r="C36" t="s">
+        <v>176</v>
+      </c>
+      <c r="D36" t="s">
+        <v>104</v>
+      </c>
+      <c r="E36" t="s">
+        <v>80</v>
+      </c>
+      <c r="F36" t="s">
+        <v>81</v>
+      </c>
+      <c r="G36">
+        <v>6</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36" t="s">
+        <v>96</v>
+      </c>
+      <c r="J36" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" t="s">
+        <v>177</v>
+      </c>
+      <c r="B37" t="s">
+        <v>65</v>
+      </c>
+      <c r="C37" t="s">
+        <v>178</v>
+      </c>
+      <c r="D37" t="s">
+        <v>179</v>
+      </c>
+      <c r="E37" t="s">
+        <v>149</v>
+      </c>
+      <c r="F37" t="s">
+        <v>106</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>4</v>
+      </c>
+      <c r="I37" t="s">
+        <v>180</v>
+      </c>
+      <c r="J37" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" t="s">
+        <v>181</v>
+      </c>
+      <c r="B38" t="s">
+        <v>67</v>
+      </c>
+      <c r="C38" t="s">
+        <v>145</v>
+      </c>
+      <c r="D38" t="s">
+        <v>88</v>
+      </c>
+      <c r="E38" t="s">
+        <v>80</v>
+      </c>
+      <c r="F38" t="s">
+        <v>81</v>
+      </c>
+      <c r="G38" t="s">
+        <v>182</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38" t="s">
+        <v>82</v>
+      </c>
+      <c r="J38" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" t="s">
+        <v>183</v>
+      </c>
+      <c r="B39" t="s">
+        <v>67</v>
+      </c>
+      <c r="C39" t="s">
+        <v>184</v>
+      </c>
+      <c r="D39" t="s">
+        <v>185</v>
+      </c>
+      <c r="E39" t="s">
+        <v>186</v>
+      </c>
+      <c r="F39" t="s">
+        <v>106</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>6</v>
+      </c>
+      <c r="I39" t="s">
+        <v>180</v>
+      </c>
+      <c r="J39" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" t="s">
+        <v>217</v>
+      </c>
+      <c r="B40" t="s">
+        <v>188</v>
+      </c>
+      <c r="C40" t="s">
+        <v>218</v>
+      </c>
+      <c r="D40" t="s">
+        <v>219</v>
+      </c>
+      <c r="E40" t="s">
+        <v>220</v>
+      </c>
+      <c r="F40" t="s">
+        <v>221</v>
+      </c>
+      <c r="G40">
+        <v>6</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40" t="s">
+        <v>222</v>
+      </c>
+      <c r="J40" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" t="s">
+        <v>223</v>
+      </c>
+      <c r="B41" t="s">
+        <v>193</v>
+      </c>
+      <c r="C41" t="s">
+        <v>224</v>
+      </c>
+      <c r="D41" t="s">
+        <v>225</v>
+      </c>
+      <c r="E41" t="s">
+        <v>220</v>
+      </c>
+      <c r="F41" t="s">
+        <v>221</v>
+      </c>
+      <c r="G41">
+        <v>15</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41" t="s">
+        <v>222</v>
+      </c>
+      <c r="J41" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" t="s">
+        <v>226</v>
+      </c>
+      <c r="B42" t="s">
+        <v>195</v>
+      </c>
+      <c r="C42" t="s">
+        <v>227</v>
+      </c>
+      <c r="D42" t="s">
+        <v>228</v>
+      </c>
+      <c r="E42" t="s">
+        <v>220</v>
+      </c>
+      <c r="F42" t="s">
+        <v>221</v>
+      </c>
+      <c r="G42">
+        <v>8</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42" t="s">
+        <v>222</v>
+      </c>
+      <c r="J42" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" t="s">
+        <v>229</v>
+      </c>
+      <c r="B43" t="s">
+        <v>195</v>
+      </c>
+      <c r="C43" t="s">
+        <v>230</v>
+      </c>
+      <c r="D43" t="s">
+        <v>231</v>
+      </c>
+      <c r="E43" t="s">
+        <v>232</v>
+      </c>
+      <c r="F43" t="s">
+        <v>233</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43" t="s">
+        <v>234</v>
+      </c>
+      <c r="J43" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" t="s">
+        <v>235</v>
+      </c>
+      <c r="B44" t="s">
+        <v>197</v>
+      </c>
+      <c r="C44" t="s">
+        <v>236</v>
+      </c>
+      <c r="D44" t="s">
+        <v>237</v>
+      </c>
+      <c r="E44" t="s">
+        <v>220</v>
+      </c>
+      <c r="F44" t="s">
+        <v>221</v>
+      </c>
+      <c r="G44">
+        <v>6</v>
+      </c>
+      <c r="H44">
+        <v>3</v>
+      </c>
+      <c r="I44" t="s">
+        <v>222</v>
+      </c>
+      <c r="J44" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" t="s">
+        <v>238</v>
+      </c>
+      <c r="B45" t="s">
+        <v>197</v>
+      </c>
+      <c r="C45" t="s">
+        <v>239</v>
+      </c>
+      <c r="D45" t="s">
+        <v>240</v>
+      </c>
+      <c r="E45" t="s">
+        <v>232</v>
+      </c>
+      <c r="F45" t="s">
+        <v>233</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>3</v>
+      </c>
+      <c r="I45" t="s">
+        <v>241</v>
+      </c>
+      <c r="J45" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" t="s">
+        <v>242</v>
+      </c>
+      <c r="B46" t="s">
+        <v>200</v>
+      </c>
+      <c r="C46" t="s">
+        <v>243</v>
+      </c>
+      <c r="D46" t="s">
+        <v>240</v>
+      </c>
+      <c r="E46" t="s">
+        <v>244</v>
+      </c>
+      <c r="F46" t="s">
+        <v>221</v>
+      </c>
+      <c r="G46">
+        <v>5</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46" t="s">
+        <v>222</v>
+      </c>
+      <c r="J46" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" t="s">
+        <v>245</v>
+      </c>
+      <c r="B47" t="s">
+        <v>200</v>
+      </c>
+      <c r="C47" t="s">
+        <v>218</v>
+      </c>
+      <c r="D47" t="s">
+        <v>246</v>
+      </c>
+      <c r="E47" t="s">
+        <v>220</v>
+      </c>
+      <c r="F47" t="s">
+        <v>221</v>
+      </c>
+      <c r="G47">
+        <v>6</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47" t="s">
+        <v>222</v>
+      </c>
+      <c r="J47" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" t="s">
+        <v>247</v>
+      </c>
+      <c r="B48" t="s">
+        <v>202</v>
+      </c>
+      <c r="C48" t="s">
+        <v>248</v>
+      </c>
+      <c r="D48" t="s">
+        <v>225</v>
+      </c>
+      <c r="E48" t="s">
+        <v>249</v>
+      </c>
+      <c r="F48" t="s">
+        <v>221</v>
+      </c>
+      <c r="G48">
+        <v>5</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48" t="s">
+        <v>222</v>
+      </c>
+      <c r="J48" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" t="s">
+        <v>250</v>
+      </c>
+      <c r="B49" t="s">
+        <v>202</v>
+      </c>
+      <c r="C49" t="s">
+        <v>251</v>
+      </c>
+      <c r="D49" t="s">
+        <v>252</v>
+      </c>
+      <c r="E49" t="s">
+        <v>232</v>
+      </c>
+      <c r="F49" t="s">
+        <v>233</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49" t="s">
+        <v>253</v>
+      </c>
+      <c r="J49" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" t="s">
+        <v>254</v>
+      </c>
+      <c r="B50" t="s">
+        <v>204</v>
+      </c>
+      <c r="C50" t="s">
+        <v>255</v>
+      </c>
+      <c r="D50" t="s">
+        <v>256</v>
+      </c>
+      <c r="E50" t="s">
+        <v>220</v>
+      </c>
+      <c r="F50" t="s">
+        <v>221</v>
+      </c>
+      <c r="G50">
+        <v>6</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50" t="s">
+        <v>222</v>
+      </c>
+      <c r="J50" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" t="s">
+        <v>257</v>
+      </c>
+      <c r="B51" t="s">
+        <v>204</v>
+      </c>
+      <c r="C51" t="s">
+        <v>222</v>
+      </c>
+      <c r="D51" t="s">
+        <v>222</v>
+      </c>
+      <c r="E51" t="s">
+        <v>258</v>
+      </c>
+      <c r="F51" t="s">
+        <v>222</v>
+      </c>
+      <c r="G51">
+        <v>5</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51" t="s">
+        <v>222</v>
+      </c>
+      <c r="J51" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" t="s">
+        <v>259</v>
+      </c>
+      <c r="B52" t="s">
+        <v>204</v>
+      </c>
+      <c r="C52" t="s">
+        <v>260</v>
+      </c>
+      <c r="D52" t="s">
+        <v>231</v>
+      </c>
+      <c r="E52" t="s">
+        <v>261</v>
+      </c>
+      <c r="F52" t="s">
+        <v>233</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>4</v>
+      </c>
+      <c r="I52" t="s">
+        <v>222</v>
+      </c>
+      <c r="J52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" t="s">
+        <v>262</v>
+      </c>
+      <c r="B53" t="s">
+        <v>206</v>
+      </c>
+      <c r="C53" t="s">
+        <v>224</v>
+      </c>
+      <c r="D53" t="s">
+        <v>263</v>
+      </c>
+      <c r="E53" t="s">
+        <v>220</v>
+      </c>
+      <c r="F53" t="s">
+        <v>221</v>
+      </c>
+      <c r="G53">
+        <v>22</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53" t="s">
+        <v>222</v>
+      </c>
+      <c r="J53" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" t="s">
+        <v>264</v>
+      </c>
+      <c r="B54" t="s">
+        <v>206</v>
+      </c>
+      <c r="C54" t="s">
+        <v>265</v>
+      </c>
+      <c r="D54" t="s">
+        <v>266</v>
+      </c>
+      <c r="E54" t="s">
+        <v>267</v>
+      </c>
+      <c r="F54" t="s">
+        <v>221</v>
+      </c>
+      <c r="G54">
+        <v>4</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54" t="s">
+        <v>222</v>
+      </c>
+      <c r="J54" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" t="s">
+        <v>268</v>
+      </c>
+      <c r="B55" t="s">
+        <v>208</v>
+      </c>
+      <c r="C55" t="s">
+        <v>269</v>
+      </c>
+      <c r="D55" t="s">
+        <v>266</v>
+      </c>
+      <c r="E55" t="s">
+        <v>220</v>
+      </c>
+      <c r="F55" t="s">
+        <v>221</v>
+      </c>
+      <c r="G55">
+        <v>8</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55" t="s">
+        <v>222</v>
+      </c>
+      <c r="J55" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" t="s">
+        <v>270</v>
+      </c>
+      <c r="B56" t="s">
+        <v>208</v>
+      </c>
+      <c r="C56" t="s">
+        <v>222</v>
+      </c>
+      <c r="D56" t="s">
+        <v>222</v>
+      </c>
+      <c r="E56" t="s">
+        <v>258</v>
+      </c>
+      <c r="F56" t="s">
+        <v>222</v>
+      </c>
+      <c r="G56">
+        <v>4</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56" t="s">
+        <v>222</v>
+      </c>
+      <c r="J56" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" t="s">
+        <v>271</v>
+      </c>
+      <c r="B57" t="s">
+        <v>208</v>
+      </c>
+      <c r="C57" t="s">
+        <v>230</v>
+      </c>
+      <c r="D57" t="s">
+        <v>272</v>
+      </c>
+      <c r="E57" t="s">
+        <v>232</v>
+      </c>
+      <c r="F57" t="s">
+        <v>233</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57" t="s">
+        <v>273</v>
+      </c>
+      <c r="J57" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" t="s">
+        <v>274</v>
+      </c>
+      <c r="B58" t="s">
+        <v>210</v>
+      </c>
+      <c r="C58" t="s">
+        <v>275</v>
+      </c>
+      <c r="D58" t="s">
+        <v>276</v>
+      </c>
+      <c r="E58" t="s">
+        <v>220</v>
+      </c>
+      <c r="F58" t="s">
+        <v>221</v>
+      </c>
+      <c r="G58">
+        <v>9</v>
+      </c>
+      <c r="H58">
+        <v>3</v>
+      </c>
+      <c r="I58" t="s">
+        <v>222</v>
+      </c>
+      <c r="J58" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" t="s">
+        <v>277</v>
+      </c>
+      <c r="B59" t="s">
+        <v>210</v>
+      </c>
+      <c r="C59" t="s">
+        <v>222</v>
+      </c>
+      <c r="D59" t="s">
+        <v>222</v>
+      </c>
+      <c r="E59" t="s">
+        <v>232</v>
+      </c>
+      <c r="F59" t="s">
+        <v>222</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59" t="s">
+        <v>278</v>
+      </c>
+      <c r="J59" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" t="s">
+        <v>279</v>
+      </c>
+      <c r="B60" t="s">
+        <v>210</v>
+      </c>
+      <c r="C60" t="s">
+        <v>239</v>
+      </c>
+      <c r="D60" t="s">
+        <v>276</v>
+      </c>
+      <c r="E60" t="s">
+        <v>232</v>
+      </c>
+      <c r="F60" t="s">
+        <v>233</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>5</v>
+      </c>
+      <c r="I60" t="s">
+        <v>280</v>
+      </c>
+      <c r="J60" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" t="s">
+        <v>281</v>
+      </c>
+      <c r="B61" t="s">
+        <v>212</v>
+      </c>
+      <c r="C61" t="s">
+        <v>282</v>
+      </c>
+      <c r="D61" t="s">
+        <v>283</v>
+      </c>
+      <c r="E61" t="s">
+        <v>244</v>
+      </c>
+      <c r="F61" t="s">
+        <v>221</v>
+      </c>
+      <c r="G61">
+        <v>8</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61" t="s">
+        <v>222</v>
+      </c>
+      <c r="J61" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" t="s">
+        <v>284</v>
+      </c>
+      <c r="B62" t="s">
+        <v>212</v>
+      </c>
+      <c r="C62" t="s">
+        <v>285</v>
+      </c>
+      <c r="D62" t="s">
+        <v>286</v>
+      </c>
+      <c r="E62" t="s">
+        <v>287</v>
+      </c>
+      <c r="F62" t="s">
+        <v>221</v>
+      </c>
+      <c r="G62">
+        <v>8</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62" t="s">
+        <v>222</v>
+      </c>
+      <c r="J62" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" t="s">
+        <v>288</v>
+      </c>
+      <c r="B63" t="s">
+        <v>214</v>
+      </c>
+      <c r="C63" t="s">
+        <v>289</v>
+      </c>
+      <c r="D63" t="s">
+        <v>290</v>
+      </c>
+      <c r="E63" t="s">
+        <v>291</v>
+      </c>
+      <c r="F63" t="s">
+        <v>221</v>
+      </c>
+      <c r="G63">
+        <v>6</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63" t="s">
+        <v>222</v>
+      </c>
+      <c r="J63" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" t="s">
+        <v>292</v>
+      </c>
+      <c r="B64" t="s">
+        <v>214</v>
+      </c>
+      <c r="C64" t="s">
+        <v>251</v>
+      </c>
+      <c r="D64" t="s">
+        <v>293</v>
+      </c>
+      <c r="E64" t="s">
+        <v>232</v>
+      </c>
+      <c r="F64" t="s">
+        <v>233</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64" t="s">
+        <v>294</v>
+      </c>
+      <c r="J64" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" t="s">
+        <v>295</v>
+      </c>
+      <c r="B65" t="s">
+        <v>216</v>
+      </c>
+      <c r="C65" t="s">
+        <v>296</v>
+      </c>
+      <c r="D65" t="s">
+        <v>293</v>
+      </c>
+      <c r="E65" t="s">
+        <v>267</v>
+      </c>
+      <c r="F65" t="s">
+        <v>221</v>
+      </c>
+      <c r="G65">
+        <v>8</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65" t="s">
+        <v>222</v>
+      </c>
+      <c r="J65" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" t="s">
+        <v>297</v>
+      </c>
+      <c r="B66" t="s">
+        <v>216</v>
+      </c>
+      <c r="C66" t="s">
+        <v>260</v>
+      </c>
+      <c r="D66" t="s">
+        <v>298</v>
+      </c>
+      <c r="E66" t="s">
+        <v>299</v>
+      </c>
+      <c r="F66" t="s">
+        <v>233</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>5</v>
+      </c>
+      <c r="I66" t="s">
+        <v>222</v>
+      </c>
+      <c r="J66" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -3051,5 +7480,18 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>